--- a/data/trans_orig/Q5403-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5403-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2007</t>
+          <t>Población según si es capaz de ir de compras en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39165</t>
+          <t>39409</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66592</t>
+          <t>70584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56069</t>
+          <t>54956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87780</t>
+          <t>88033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66052</t>
+          <t>67096</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100219</t>
+          <t>101838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97320</t>
+          <t>97057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136020</t>
+          <t>138345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310169</t>
+          <t>309846</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>334853</t>
+          <t>334132</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>432908</t>
+          <t>431827</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>472078</t>
+          <t>471945</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>750439</t>
+          <t>748981</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>798703</t>
+          <t>796825</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>20233</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76164</t>
+          <t>76257</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85487</t>
+          <t>85528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>46440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58546</t>
+          <t>58126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125895</t>
+          <t>126158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141547</t>
+          <t>141564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31332</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40260</t>
+          <t>40263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>24520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50793</t>
+          <t>50963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62812</t>
+          <t>63412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>29372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72099</t>
+          <t>70741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60585</t>
+          <t>60298</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93486</t>
+          <t>94026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30079</t>
+          <t>28795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>52318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77246</t>
+          <t>79436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114089</t>
+          <t>113814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114138</t>
+          <t>115493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158736</t>
+          <t>158559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>426337</t>
+          <t>426981</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>454418</t>
+          <t>455129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>502123</t>
+          <t>503019</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>548181</t>
+          <t>548479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>941049</t>
+          <t>942631</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>993005</t>
+          <t>993334</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2012</t>
+          <t>Población según si es capaz de ir de compras en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34715</t>
+          <t>33908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62653</t>
+          <t>62879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85491</t>
+          <t>85457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123503</t>
+          <t>124086</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127323</t>
+          <t>125904</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174278</t>
+          <t>172585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>35097</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62169</t>
+          <t>62855</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75945</t>
+          <t>75224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113581</t>
+          <t>112551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118661</t>
+          <t>117934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162948</t>
+          <t>165170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>302413</t>
+          <t>300115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337353</t>
+          <t>338168</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>413233</t>
+          <t>411090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>460688</t>
+          <t>461314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>729404</t>
+          <t>730142</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>790453</t>
+          <t>789388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94163</t>
+          <t>93355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>109702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62457</t>
+          <t>62065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76534</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160712</t>
+          <t>161969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182929</t>
+          <t>182736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>37117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46786</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>66463</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91360</t>
+          <t>92277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130468</t>
+          <t>131977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,47 +4206,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>160491</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>135433</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>186699</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>12,35%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>17,63%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>160491</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>138477</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>186128</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78486</t>
+          <t>78135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83115</t>
+          <t>83962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121303</t>
+          <t>124082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>139716</t>
+          <t>138724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190193</t>
+          <t>188552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>425811</t>
+          <t>429023</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>467905</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>499287</t>
+          <t>499500</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>550116</t>
+          <t>550849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>947143</t>
+          <t>943208</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1010124</t>
+          <t>1007575</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2016</t>
+          <t>Población según si es capaz de ir de compras en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23350</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42532</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>46801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79282</t>
+          <t>79588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73896</t>
+          <t>75129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113709</t>
+          <t>114200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43360</t>
+          <t>40737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74645</t>
+          <t>76417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114717</t>
+          <t>117395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102888</t>
+          <t>103157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147745</t>
+          <t>147497</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>276814</t>
+          <t>279298</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>304594</t>
+          <t>304623</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>375484</t>
+          <t>374569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>421533</t>
+          <t>421951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>664295</t>
+          <t>665754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>719031</t>
+          <t>718337</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>50075</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169819</t>
+          <t>169245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183932</t>
+          <t>183772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139488</t>
+          <t>138987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164183</t>
+          <t>163827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312743</t>
+          <t>314648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>342368</t>
+          <t>343532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,62 +5790,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>8212</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>9009</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>32342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>40591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>32404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58925</t>
+          <t>58992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71177</t>
+          <t>72127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51144</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53715</t>
+          <t>55102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90180</t>
+          <t>90265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90086</t>
+          <t>90430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132074</t>
+          <t>131705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32252</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56614</t>
+          <t>54849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103333</t>
+          <t>103010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148796</t>
+          <t>147573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142176</t>
+          <t>141494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>192554</t>
+          <t>195040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>489630</t>
+          <t>491461</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>521034</t>
+          <t>523097</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>553697</t>
+          <t>554258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>608142</t>
+          <t>606258</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1057690</t>
+          <t>1056586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1119505</t>
+          <t>1118317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2023</t>
+          <t>Población según si es capaz de ir de compras en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>26845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>43904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99731</t>
+          <t>99367</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126760</t>
+          <t>126758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132499</t>
+          <t>131376</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164889</t>
+          <t>163838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29188</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46805</t>
+          <t>47207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92575</t>
+          <t>91080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117684</t>
+          <t>117796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126580</t>
+          <t>126488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158509</t>
+          <t>156779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183393</t>
+          <t>183681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206488</t>
+          <t>205993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266786</t>
+          <t>266647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>298189</t>
+          <t>298039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>460096</t>
+          <t>459812</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>498411</t>
+          <t>498654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14816</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>59156</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>21795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71948</t>
+          <t>71486</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>235474</t>
+          <t>236248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>252121</t>
+          <t>252675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>371428</t>
+          <t>371412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>440844</t>
+          <t>441166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>623347</t>
+          <t>624026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>699383</t>
+          <t>696237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91281</t>
+          <t>90813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100223</t>
+          <t>100214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59414</t>
+          <t>59340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67107</t>
+          <t>67024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153614</t>
+          <t>153547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165522</t>
+          <t>165178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36912</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57825</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71274</t>
+          <t>63086</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167727</t>
+          <t>166844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113263</t>
+          <t>111047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207217</t>
+          <t>207064</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51098</t>
+          <t>51414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74814</t>
+          <t>74452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76414</t>
+          <t>67225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179692</t>
+          <t>178063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132517</t>
+          <t>124428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235510</t>
+          <t>236792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>519852</t>
+          <t>520938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>550272</t>
+          <t>549498</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>685897</t>
+          <t>686674</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>879738</t>
+          <t>898506</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1235516</t>
+          <t>1235081</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421192</t>
+          <t>1429695</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5403-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5403-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39409</t>
+          <t>39005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70584</t>
+          <t>67353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54956</t>
+          <t>56262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88033</t>
+          <t>88059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43824</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67096</t>
+          <t>67524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101838</t>
+          <t>100940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97057</t>
+          <t>96043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138345</t>
+          <t>136584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>309846</t>
+          <t>307228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>334132</t>
+          <t>333810</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>431827</t>
+          <t>430112</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>471945</t>
+          <t>470405</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>748981</t>
+          <t>752560</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>796825</t>
+          <t>802176</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,48%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76257</t>
+          <t>76349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85528</t>
+          <t>85319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46440</t>
+          <t>46583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58126</t>
+          <t>58174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126158</t>
+          <t>126952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141564</t>
+          <t>141601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31460</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40263</t>
+          <t>40267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>23919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50963</t>
+          <t>50191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63412</t>
+          <t>63603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>42509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70741</t>
+          <t>73004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>58788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94026</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52318</t>
+          <t>53924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79436</t>
+          <t>78046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113814</t>
+          <t>114321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115493</t>
+          <t>112857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158559</t>
+          <t>157902</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>426981</t>
+          <t>426991</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>455129</t>
+          <t>454178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>503019</t>
+          <t>504644</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>548479</t>
+          <t>548216</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>942631</t>
+          <t>941056</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>993334</t>
+          <t>996341</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33908</t>
+          <t>34086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>61847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85457</t>
+          <t>84988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124086</t>
+          <t>123523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125904</t>
+          <t>127221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172585</t>
+          <t>174570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35097</t>
+          <t>33743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62855</t>
+          <t>62356</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75224</t>
+          <t>75570</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112551</t>
+          <t>111724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117934</t>
+          <t>116380</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165170</t>
+          <t>163307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>300115</t>
+          <t>303379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>338168</t>
+          <t>338616</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>411090</t>
+          <t>415553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>461314</t>
+          <t>460764</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>730142</t>
+          <t>728591</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>789388</t>
+          <t>790124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21731</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93355</t>
+          <t>93148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109702</t>
+          <t>109815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62065</t>
+          <t>62140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76267</t>
+          <t>76315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161969</t>
+          <t>162260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182736</t>
+          <t>183847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37294</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66463</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92277</t>
+          <t>91286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131977</t>
+          <t>133317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135433</t>
+          <t>136383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>186699</t>
+          <t>186366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>46133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78135</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83962</t>
+          <t>84835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124082</t>
+          <t>124135</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138724</t>
+          <t>139144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188552</t>
+          <t>189297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>429023</t>
+          <t>428171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>468177</t>
+          <t>469295</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>499500</t>
+          <t>501992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>550849</t>
+          <t>552324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>943208</t>
+          <t>940846</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1007575</t>
+          <t>1008581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>44318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>47139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79588</t>
+          <t>79612</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75129</t>
+          <t>77030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114200</t>
+          <t>116521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40737</t>
+          <t>41571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76417</t>
+          <t>74530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117395</t>
+          <t>113052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103157</t>
+          <t>102308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147497</t>
+          <t>145737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>279298</t>
+          <t>278606</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>304623</t>
+          <t>305254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>374569</t>
+          <t>374783</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>421951</t>
+          <t>419997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>665754</t>
+          <t>664965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>718337</t>
+          <t>718642</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>17460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25693</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50075</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169245</t>
+          <t>168674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183772</t>
+          <t>183038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138987</t>
+          <t>138734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163827</t>
+          <t>163815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314648</t>
+          <t>314425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343532</t>
+          <t>342610</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32404</t>
+          <t>32386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58992</t>
+          <t>59208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72127</t>
+          <t>71689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>28502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51496</t>
+          <t>51700</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55102</t>
+          <t>54590</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90265</t>
+          <t>91183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90430</t>
+          <t>90475</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131705</t>
+          <t>132723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54849</t>
+          <t>54840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103010</t>
+          <t>104737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147573</t>
+          <t>149322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141494</t>
+          <t>142571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195040</t>
+          <t>193854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>491461</t>
+          <t>492637</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>523097</t>
+          <t>522974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>554258</t>
+          <t>552881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>606258</t>
+          <t>607147</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1056586</t>
+          <t>1058749</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1118317</t>
+          <t>1121509</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34951</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26845</t>
+          <t>27964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43904</t>
+          <t>45387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>112916</t>
+          <t>121933</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99367</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126758</t>
+          <t>136499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>147867</t>
+          <t>158153</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131376</t>
+          <t>141754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163838</t>
+          <t>175633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37467</t>
+          <t>40281</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28585</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47207</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>103830</t>
+          <t>111533</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91080</t>
+          <t>98343</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117796</t>
+          <t>127518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>141296</t>
+          <t>151814</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126488</t>
+          <t>134962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156779</t>
+          <t>171053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>195363</t>
+          <t>212012</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183681</t>
+          <t>199381</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>205993</t>
+          <t>224396</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>283987</t>
+          <t>305315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266647</t>
+          <t>289345</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>298039</t>
+          <t>323099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>479349</t>
+          <t>517326</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>459812</t>
+          <t>495593</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>498654</t>
+          <t>537407</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>267781</t>
+          <t>288513</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>267781</t>
+          <t>288513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>267781</t>
+          <t>288513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>768513</t>
+          <t>827294</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>768513</t>
+          <t>827294</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>768513</t>
+          <t>827294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28550</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>25593</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>29936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29252</t>
+          <t>34123</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>26876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59156</t>
+          <t>42765</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>48428</t>
+          <t>55369</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21795</t>
+          <t>45654</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71486</t>
+          <t>67254</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>244747</t>
+          <t>272843</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>236248</t>
+          <t>262300</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>252675</t>
+          <t>280580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>412401</t>
+          <t>227666</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>371412</t>
+          <t>218088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>441166</t>
+          <t>236145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>657147</t>
+          <t>500509</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>624026</t>
+          <t>485526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>696237</t>
+          <t>511925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>484</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96509</t>
+          <t>108954</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90813</t>
+          <t>102037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100214</t>
+          <t>112968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63855</t>
+          <t>74127</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59340</t>
+          <t>69147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67024</t>
+          <t>77722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>160363</t>
+          <t>183081</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153547</t>
+          <t>175552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165178</t>
+          <t>188753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>103830</t>
+          <t>117707</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103830</t>
+          <t>117707</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103830</t>
+          <t>117707</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>175155</t>
+          <t>200562</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>175155</t>
+          <t>200562</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175155</t>
+          <t>200562</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45908</t>
+          <t>48232</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36815</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56489</t>
+          <t>59187</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>128602</t>
+          <t>139614</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>124673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166844</t>
+          <t>156346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>174510</t>
+          <t>187845</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111047</t>
+          <t>170112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207064</t>
+          <t>208380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -8374,27 +8374,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62341</t>
+          <t>68005</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51414</t>
+          <t>55779</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74452</t>
+          <t>82012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>138953</t>
+          <t>152560</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67225</t>
+          <t>135539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>178063</t>
+          <t>167911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>201294</t>
+          <t>220565</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124428</t>
+          <t>199949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236792</t>
+          <t>241504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536618</t>
+          <t>593808</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>520938</t>
+          <t>578020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>549498</t>
+          <t>608860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760242</t>
+          <t>607108</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>686674</t>
+          <t>586604</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>898506</t>
+          <t>627172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1296860</t>
+          <t>1200916</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1235081</t>
+          <t>1173517</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1429695</t>
+          <t>1225117</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>644867</t>
+          <t>710045</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>644867</t>
+          <t>710045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>644867</t>
+          <t>710045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1672664</t>
+          <t>1609327</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1672664</t>
+          <t>1609327</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1672664</t>
+          <t>1609327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
